--- a/JsonConverter/ExcelFiles/DNDialogueGroup.xlsx
+++ b/JsonConverter/ExcelFiles/DNDialogueGroup.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.535"/>
+  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.12458"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\UnityBasic_6\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294936010" windowHeight="16740"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="21720" windowHeight="11490"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>
@@ -21,19 +21,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <x:si>
-    <x:t>dialogue_group_mainstream_1_2_100,dialogue_group_mainstream_1_2_200,dialogue_group_mainstream_1_2_300,dialogue_group_mainstream_1_2_400</x:t>
+    <x:t>npc_shop_hellena_success_buyItem_1</x:t>
   </x:si>
   <x:si>
-    <x:t>DialogueIdList</x:t>
+    <x:t>dialogue_group_mainstream_1_1</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">상점-헬레나 구매 성공 </x:t>
+    <x:t>dialogue_group_mainstream_1_3</x:t>
   </x:si>
   <x:si>
-    <x:t>메인스트림 1_1챕터 그룹</x:t>
+    <x:t>dialogue_group_mainstream_1_2</x:t>
   </x:si>
   <x:si>
-    <x:t>상점-헬레나 상점 오픈</x:t>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainstream_1_1_100,dialogue_mainstream_1_1_200.dialogue_mainstream_1_1_300</x:t>
   </x:si>
   <x:si>
     <x:t>메인스트림 1_2챕터 그룹</x:t>
@@ -42,34 +45,31 @@
     <x:t>메인스트림 1_3챕터 그룹</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_mainstream_1_1_100,dialogue_mainstream_1_1_200.dialogue_mainstream_1_1_300</x:t>
+    <x:t>DialogueIdList</x:t>
   </x:si>
   <x:si>
-    <x:t>string[]</x:t>
+    <x:t>상점-헬레나 상점 오픈</x:t>
+  </x:si>
+  <x:si>
+    <x:t>메인스트림 1_1챕터 그룹</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">상점-헬레나 구매 성공 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
   </x:si>
   <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_group_mainstream_1_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainstream_1_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>npc_shop_hellena_success_buyItem_1</x:t>
+    <x:t>dialogue_group_mainstream_1_2_100,dialogue_group_mainstream_1_2_200,dialogue_group_mainstream_1_2_300,dialogue_group_mainstream_1_2_400</x:t>
   </x:si>
   <x:si>
     <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
   </x:si>
   <x:si>
     <x:t>string</x:t>
@@ -82,7 +82,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="7">
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
@@ -114,12 +114,7 @@
       <x:color rgb="ff000000"/>
     </x:font>
     <x:font>
-      <x:name val="&quot;맑은 고딕&quot;"/>
-      <x:sz val="10"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="&quot;맑은 고딕&quot;"/>
+      <x:name val="Arial"/>
       <x:sz val="11"/>
       <x:color rgb="ff008000"/>
     </x:font>
@@ -130,18 +125,6 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffc6efce"/>
-        <x:bgColor rgb="ffc6efce"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffffffff"/>
-        <x:bgColor rgb="ff4d93d9"/>
-      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -158,6 +141,18 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffffffff"/>
+        <x:bgColor rgb="ff4d93d9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="ffc6efce"/>
+        <x:bgColor rgb="ffc6efce"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="ffffffff"/>
         <x:bgColor indexed="64"/>
       </x:patternFill>
     </x:fill>
@@ -165,16 +160,16 @@
   <x:borders count="2">
     <x:border>
       <x:left>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:left>
       <x:right>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:right>
       <x:top>
         <x:color auto="1"/>
       </x:top>
       <x:bottom>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -197,49 +192,450 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="13">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="표준" xfId="0" builtinId="0"/>
   </x:cellStyles>
-  <x:dxfs count="0"/>
-  <x:tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <x:dxfs count="12">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd7dff4"/>
+              <x:bgColor rgb="ffd7dff4"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+            <x:vertical style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:vertical>
+            <x:horizontal style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ffd7dff4"/>
+              <x:bgColor rgb="ffd7dff4"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:left style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:left>
+            <x:right style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:right>
+            <x:top style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+            <x:bottom style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+            <x:vertical style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:vertical>
+            <x:horizontal style="thin">
+              <x:color rgb="ffffffff"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf/>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ffaebfea"/>
+          <x:bgColor rgb="ffaebfea"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:top style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ffffffff"/>
+            <x:b val="1"/>
+          </x:font>
+          <x:fill>
+            <x:patternFill patternType="solid">
+              <x:fgColor rgb="ff6182d6"/>
+              <x:bgColor rgb="ff6182d6"/>
+            </x:patternFill>
+          </x:fill>
+          <x:border>
+            <x:bottom style="thick">
+              <x:color rgb="ffffffff"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:left>
+              <x:color auto="1"/>
+            </x:left>
+            <x:right>
+              <x:color auto="1"/>
+            </x:right>
+            <x:top style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+            <x:vertical>
+              <x:color auto="1"/>
+            </x:vertical>
+            <x:horizontal>
+              <x:color auto="1"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:color rgb="ff000000"/>
+          </x:font>
+          <x:border>
+            <x:left>
+              <x:color auto="1"/>
+            </x:left>
+            <x:right>
+              <x:color auto="1"/>
+            </x:right>
+            <x:top style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+            <x:vertical>
+              <x:color auto="1"/>
+            </x:vertical>
+            <x:horizontal>
+              <x:color auto="1"/>
+            </x:horizontal>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ff94a5df"/>
+          <x:bgColor rgb="ff94a5df"/>
+        </x:patternFill>
+      </x:fill>
+      <x:border>
+        <x:top style="thin">
+          <x:color rgb="ff6182d6"/>
+        </x:top>
+        <x:bottom style="thin">
+          <x:color rgb="ff6182d6"/>
+        </x:bottom>
+      </x:border>
+    </x:dxf>
+    <x:dxf>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:fgColor rgb="ff6182d6"/>
+          <x:bgColor rgb="ff6182d6"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:top style="thin">
+              <x:color rgb="ff6182d6"/>
+            </x:top>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:hs="http://schemas.haansoft.com/office/spreadsheet/8.0" Requires="hs">
+        <x:dxf hs:applyExtension="1">
+          <x:font hs:extension="1">
+            <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
+            <hs:size val="0"/>
+            <hs:ratio val="0"/>
+            <hs:spacing val="0"/>
+            <hs:offset val="0"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Choice>
+      <mc:Fallback>
+        <x:dxf>
+          <x:font>
+            <x:b val="1"/>
+          </x:font>
+          <x:border>
+            <x:bottom style="medium">
+              <x:color rgb="ff6182d6"/>
+            </x:bottom>
+          </x:border>
+        </x:dxf>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </x:dxfs>
+  <x:tableStyles count="2" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <x:tableStyle name="Normal Style 1 - Accent 1" pivot="0" table="1" count="9">
+      <x:tableStyleElement type="wholeTable" size="1" dxfId="0"/>
+      <x:tableStyleElement type="headerRow" size="1" dxfId="5"/>
+      <x:tableStyleElement type="totalRow" size="1" dxfId="4"/>
+      <x:tableStyleElement type="firstColumn" size="1" dxfId="3"/>
+      <x:tableStyleElement type="lastColumn" size="1" dxfId="3"/>
+      <x:tableStyleElement type="firstRowStripe" size="1" dxfId="2"/>
+      <x:tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
+      <x:tableStyleElement type="firstColumnStripe" size="1" dxfId="2"/>
+      <x:tableStyleElement type="secondColumnStripe" size="1" dxfId="1"/>
+    </x:tableStyle>
+    <x:tableStyle name="Light Style 1 - Accent 1" pivot="1" table="0" count="8">
+      <x:tableStyleElement type="wholeTable" size="1" dxfId="6"/>
+      <x:tableStyleElement type="headerRow" size="1" dxfId="11"/>
+      <x:tableStyleElement type="totalRow" size="1" dxfId="10"/>
+      <x:tableStyleElement type="firstColumn" size="1" dxfId="9"/>
+      <x:tableStyleElement type="lastColumn" size="1" dxfId="9"/>
+      <x:tableStyleElement type="firstRowStripe" size="1" dxfId="7"/>
+      <x:tableStyleElement type="secondRowStripe" size="1" dxfId="1"/>
+      <x:tableStyleElement type="firstColumnStripe" size="1" dxfId="8"/>
+    </x:tableStyle>
+  </x:tableStyles>
 </x:styleSheet>
 </file>
 
@@ -439,380 +835,441 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr codeName="Sheet1">
-    <x:outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
-  </x:sheetPr>
+  <x:sheetPr codeName="Sheet1"/>
   <x:dimension ref="A1:O35"/>
   <x:sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="1" width="32.26953125" customWidth="1"/>
-    <x:col min="2" max="2" width="25.7265625" customWidth="1"/>
-    <x:col min="3" max="3" width="104.26953125" customWidth="1"/>
-    <x:col min="5" max="5" width="30.54296875" customWidth="1"/>
+    <x:col min="1" max="1" width="32.26953125" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="25.7265625" style="1" customWidth="1"/>
+    <x:col min="3" max="3" width="142" style="1" customWidth="1"/>
+    <x:col min="5" max="5" width="30.54296875" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A1" s="1" t="s">
+    <x:row r="1" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A1" s="6" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B1" s="6"/>
+      <x:c r="C1" s="6"/>
+      <x:c r="D1" s="7"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="7"/>
+    </x:row>
+    <x:row r="2" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A2" s="6" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B1" s="1"/>
-      <x:c r="C1" s="1"/>
-    </x:row>
-    <x:row r="2" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A2" s="1" t="s">
+      <x:c r="B2" s="6" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D2" s="7"/>
+      <x:c r="E2" s="2"/>
+      <x:c r="F2" s="7"/>
+    </x:row>
+    <x:row r="3" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A3" s="8" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>17</x:v>
+      <x:c r="B3" s="8" t="s">
+        <x:v>13</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
+      <x:c r="C3" s="8" t="s">
         <x:v>8</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A3" s="2" t="s">
+      <x:c r="D3" s="7"/>
+      <x:c r="E3" s="2"/>
+      <x:c r="F3" s="7"/>
+    </x:row>
+    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A4" s="9" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B4" s="9" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C4" s="9" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D4" s="2"/>
+      <x:c r="E4" s="2"/>
+      <x:c r="F4" s="2"/>
+      <x:c r="G4" s="2"/>
+      <x:c r="H4" s="2"/>
+      <x:c r="I4" s="2"/>
+      <x:c r="J4" s="2"/>
+      <x:c r="K4" s="2"/>
+      <x:c r="L4" s="2"/>
+      <x:c r="M4" s="2"/>
+      <x:c r="N4" s="2"/>
+      <x:c r="O4" s="2"/>
+    </x:row>
+    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A5" s="9" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B5" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C5" s="10" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D5" s="2"/>
+      <x:c r="E5" s="2"/>
+      <x:c r="F5" s="2"/>
+      <x:c r="G5" s="2"/>
+      <x:c r="H5" s="2"/>
+      <x:c r="I5" s="2"/>
+      <x:c r="J5" s="2"/>
+      <x:c r="K5" s="2"/>
+      <x:c r="L5" s="2"/>
+      <x:c r="M5" s="2"/>
+      <x:c r="N5" s="2"/>
+      <x:c r="O5" s="2"/>
+    </x:row>
+    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A6" s="10" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B6" s="10" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C6" s="10"/>
+      <x:c r="D6" s="2"/>
+      <x:c r="E6" s="2"/>
+      <x:c r="F6" s="2"/>
+      <x:c r="G6" s="2"/>
+      <x:c r="H6" s="2"/>
+      <x:c r="I6" s="2"/>
+      <x:c r="J6" s="2"/>
+      <x:c r="K6" s="2"/>
+      <x:c r="L6" s="2"/>
+      <x:c r="M6" s="2"/>
+      <x:c r="N6" s="2"/>
+      <x:c r="O6" s="2"/>
+    </x:row>
+    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A7" s="9" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B7" s="9" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>15</x:v>
+      <x:c r="C7" s="9"/>
+      <x:c r="D7" s="2"/>
+      <x:c r="E7" s="2"/>
+      <x:c r="F7" s="2"/>
+      <x:c r="G7" s="2"/>
+      <x:c r="H7" s="2"/>
+      <x:c r="I7" s="2"/>
+      <x:c r="J7" s="2"/>
+      <x:c r="K7" s="2"/>
+      <x:c r="L7" s="2"/>
+      <x:c r="M7" s="2"/>
+      <x:c r="N7" s="2"/>
+      <x:c r="O7" s="2"/>
+    </x:row>
+    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A8" s="9" t="s">
+        <x:v>0</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A4" s="4" t="s">
+      <x:c r="B8" s="11" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D4" s="3"/>
-      <x:c r="E4" s="3"/>
-      <x:c r="F4" s="3"/>
-      <x:c r="G4" s="3"/>
-      <x:c r="H4" s="3"/>
-      <x:c r="I4" s="3"/>
-      <x:c r="J4" s="3"/>
-      <x:c r="K4" s="3"/>
-      <x:c r="L4" s="3"/>
-      <x:c r="M4" s="3"/>
-      <x:c r="N4" s="3"/>
-      <x:c r="O4" s="3"/>
-    </x:row>
-    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A5" s="4" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="5" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="3"/>
-      <x:c r="E5" s="3"/>
-      <x:c r="F5" s="3"/>
-      <x:c r="G5" s="3"/>
-      <x:c r="H5" s="3"/>
-      <x:c r="I5" s="3"/>
-      <x:c r="J5" s="3"/>
-      <x:c r="K5" s="3"/>
-      <x:c r="L5" s="3"/>
-      <x:c r="M5" s="3"/>
-      <x:c r="N5" s="3"/>
-      <x:c r="O5" s="3"/>
-    </x:row>
-    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A6" s="5" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C6" s="5"/>
-      <x:c r="D6" s="3"/>
-      <x:c r="E6" s="3"/>
-      <x:c r="F6" s="3"/>
-      <x:c r="G6" s="3"/>
-      <x:c r="H6" s="3"/>
-      <x:c r="I6" s="3"/>
-      <x:c r="J6" s="3"/>
-      <x:c r="K6" s="3"/>
-      <x:c r="L6" s="3"/>
-      <x:c r="M6" s="3"/>
-      <x:c r="N6" s="3"/>
-      <x:c r="O6" s="3"/>
-    </x:row>
-    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A7" s="4" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B7" s="4" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="4"/>
-      <x:c r="D7" s="3"/>
-      <x:c r="E7" s="3"/>
-      <x:c r="F7" s="3"/>
-      <x:c r="G7" s="3"/>
-      <x:c r="H7" s="3"/>
-      <x:c r="I7" s="3"/>
-      <x:c r="J7" s="3"/>
-      <x:c r="K7" s="3"/>
-      <x:c r="L7" s="3"/>
-      <x:c r="M7" s="3"/>
-      <x:c r="N7" s="3"/>
-      <x:c r="O7" s="3"/>
-    </x:row>
-    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A8" s="4" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B8" s="6" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="6"/>
-      <x:c r="D8" s="3"/>
-      <x:c r="E8" s="3"/>
-      <x:c r="F8" s="3"/>
-      <x:c r="G8" s="3"/>
-      <x:c r="H8" s="3"/>
-      <x:c r="I8" s="3"/>
-      <x:c r="J8" s="3"/>
-      <x:c r="K8" s="3"/>
-      <x:c r="L8" s="3"/>
-      <x:c r="M8" s="3"/>
-      <x:c r="N8" s="3"/>
-      <x:c r="O8" s="3"/>
+      <x:c r="C8" s="11"/>
+      <x:c r="D8" s="2"/>
+      <x:c r="E8" s="2"/>
+      <x:c r="F8" s="2"/>
+      <x:c r="G8" s="2"/>
+      <x:c r="H8" s="2"/>
+      <x:c r="I8" s="2"/>
+      <x:c r="J8" s="2"/>
+      <x:c r="K8" s="2"/>
+      <x:c r="L8" s="2"/>
+      <x:c r="M8" s="2"/>
+      <x:c r="N8" s="2"/>
+      <x:c r="O8" s="2"/>
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A9" s="6"/>
-      <x:c r="B9" s="6"/>
-      <x:c r="C9" s="6"/>
-      <x:c r="D9" s="3"/>
-      <x:c r="E9" s="3"/>
-      <x:c r="F9" s="3"/>
-      <x:c r="G9" s="3"/>
-      <x:c r="H9" s="3"/>
-      <x:c r="I9" s="3"/>
-      <x:c r="J9" s="3"/>
-      <x:c r="K9" s="3"/>
-      <x:c r="L9" s="3"/>
-      <x:c r="M9" s="3"/>
-      <x:c r="N9" s="3"/>
-      <x:c r="O9" s="3"/>
+      <x:c r="A9" s="11"/>
+      <x:c r="B9" s="11"/>
+      <x:c r="C9" s="11"/>
+      <x:c r="D9" s="2"/>
+      <x:c r="E9" s="2"/>
+      <x:c r="F9" s="2"/>
+      <x:c r="G9" s="2"/>
+      <x:c r="H9" s="2"/>
+      <x:c r="I9" s="2"/>
+      <x:c r="J9" s="2"/>
+      <x:c r="K9" s="2"/>
+      <x:c r="L9" s="2"/>
+      <x:c r="M9" s="2"/>
+      <x:c r="N9" s="2"/>
+      <x:c r="O9" s="2"/>
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A10" s="7"/>
-      <x:c r="B10" s="7"/>
-      <x:c r="C10" s="7"/>
-      <x:c r="D10" s="3"/>
-      <x:c r="E10" s="3"/>
-      <x:c r="F10" s="3"/>
-      <x:c r="G10" s="3"/>
-      <x:c r="H10" s="3"/>
-      <x:c r="I10" s="3"/>
-      <x:c r="J10" s="3"/>
-      <x:c r="K10" s="3"/>
-      <x:c r="L10" s="3"/>
-      <x:c r="M10" s="3"/>
-      <x:c r="N10" s="3"/>
-      <x:c r="O10" s="3"/>
+      <x:c r="A10" s="12"/>
+      <x:c r="B10" s="12"/>
+      <x:c r="C10" s="12"/>
+      <x:c r="D10" s="2"/>
+      <x:c r="E10" s="2"/>
+      <x:c r="F10" s="2"/>
+      <x:c r="G10" s="2"/>
+      <x:c r="H10" s="2"/>
+      <x:c r="I10" s="2"/>
+      <x:c r="J10" s="2"/>
+      <x:c r="K10" s="2"/>
+      <x:c r="L10" s="2"/>
+      <x:c r="M10" s="2"/>
+      <x:c r="N10" s="2"/>
+      <x:c r="O10" s="2"/>
     </x:row>
     <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A11" s="7"/>
-      <x:c r="B11" s="7"/>
-      <x:c r="C11" s="7"/>
-      <x:c r="D11" s="3"/>
-      <x:c r="E11" s="3"/>
-      <x:c r="F11" s="3"/>
-      <x:c r="G11" s="3"/>
-      <x:c r="H11" s="3"/>
-      <x:c r="I11" s="3"/>
-      <x:c r="J11" s="3"/>
-      <x:c r="K11" s="3"/>
-      <x:c r="L11" s="3"/>
-      <x:c r="M11" s="3"/>
-      <x:c r="N11" s="3"/>
-      <x:c r="O11" s="3"/>
+      <x:c r="A11" s="12"/>
+      <x:c r="B11" s="12"/>
+      <x:c r="C11" s="12"/>
+      <x:c r="D11" s="2"/>
+      <x:c r="E11" s="2"/>
+      <x:c r="F11" s="2"/>
+      <x:c r="G11" s="2"/>
+      <x:c r="H11" s="2"/>
+      <x:c r="I11" s="2"/>
+      <x:c r="J11" s="2"/>
+      <x:c r="K11" s="2"/>
+      <x:c r="L11" s="2"/>
+      <x:c r="M11" s="2"/>
+      <x:c r="N11" s="2"/>
+      <x:c r="O11" s="2"/>
     </x:row>
     <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A12" s="6"/>
-      <x:c r="B12" s="6"/>
-      <x:c r="C12" s="6"/>
-      <x:c r="D12" s="3"/>
-      <x:c r="E12" s="3"/>
-      <x:c r="F12" s="3"/>
-      <x:c r="G12" s="3"/>
-      <x:c r="H12" s="3"/>
-      <x:c r="I12" s="3"/>
-      <x:c r="J12" s="3"/>
-      <x:c r="K12" s="3"/>
-      <x:c r="L12" s="3"/>
-      <x:c r="M12" s="3"/>
-      <x:c r="N12" s="3"/>
-      <x:c r="O12" s="3"/>
+      <x:c r="A12" s="11"/>
+      <x:c r="B12" s="11"/>
+      <x:c r="C12" s="11"/>
+      <x:c r="D12" s="2"/>
+      <x:c r="E12" s="2"/>
+      <x:c r="F12" s="2"/>
+      <x:c r="G12" s="2"/>
+      <x:c r="H12" s="2"/>
+      <x:c r="I12" s="2"/>
+      <x:c r="J12" s="2"/>
+      <x:c r="K12" s="2"/>
+      <x:c r="L12" s="2"/>
+      <x:c r="M12" s="2"/>
+      <x:c r="N12" s="2"/>
+      <x:c r="O12" s="2"/>
     </x:row>
     <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A13" s="4"/>
-      <x:c r="B13" s="4"/>
-      <x:c r="C13" s="4"/>
-      <x:c r="D13" s="3"/>
-      <x:c r="E13" s="3"/>
-      <x:c r="F13" s="3"/>
-      <x:c r="G13" s="3"/>
-      <x:c r="H13" s="3"/>
-      <x:c r="I13" s="3"/>
-      <x:c r="J13" s="3"/>
-      <x:c r="K13" s="3"/>
-      <x:c r="L13" s="3"/>
-      <x:c r="M13" s="3"/>
-      <x:c r="N13" s="3"/>
-      <x:c r="O13" s="3"/>
+      <x:c r="A13" s="9"/>
+      <x:c r="B13" s="9"/>
+      <x:c r="C13" s="9"/>
+      <x:c r="D13" s="2"/>
+      <x:c r="E13" s="2"/>
+      <x:c r="F13" s="2"/>
+      <x:c r="G13" s="2"/>
+      <x:c r="H13" s="2"/>
+      <x:c r="I13" s="2"/>
+      <x:c r="J13" s="2"/>
+      <x:c r="K13" s="2"/>
+      <x:c r="L13" s="2"/>
+      <x:c r="M13" s="2"/>
+      <x:c r="N13" s="2"/>
+      <x:c r="O13" s="2"/>
     </x:row>
     <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A14" s="7"/>
-      <x:c r="B14" s="7"/>
-      <x:c r="C14" s="7"/>
-      <x:c r="D14" s="3"/>
-      <x:c r="E14" s="3"/>
-      <x:c r="F14" s="3"/>
-      <x:c r="G14" s="3"/>
-      <x:c r="H14" s="3"/>
-      <x:c r="I14" s="3"/>
-      <x:c r="J14" s="3"/>
-      <x:c r="K14" s="3"/>
-      <x:c r="L14" s="3"/>
-      <x:c r="M14" s="3"/>
-      <x:c r="N14" s="3"/>
-      <x:c r="O14" s="3"/>
+      <x:c r="A14" s="12"/>
+      <x:c r="B14" s="12"/>
+      <x:c r="C14" s="12"/>
+      <x:c r="D14" s="2"/>
+      <x:c r="E14" s="2"/>
+      <x:c r="F14" s="2"/>
+      <x:c r="G14" s="2"/>
+      <x:c r="H14" s="2"/>
+      <x:c r="I14" s="2"/>
+      <x:c r="J14" s="2"/>
+      <x:c r="K14" s="2"/>
+      <x:c r="L14" s="2"/>
+      <x:c r="M14" s="2"/>
+      <x:c r="N14" s="2"/>
+      <x:c r="O14" s="2"/>
     </x:row>
     <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A15" s="7"/>
-      <x:c r="B15" s="7"/>
-      <x:c r="C15" s="7"/>
-      <x:c r="D15" s="3"/>
-      <x:c r="E15" s="3"/>
-      <x:c r="F15" s="3"/>
-      <x:c r="G15" s="3"/>
-      <x:c r="H15" s="3"/>
-      <x:c r="I15" s="3"/>
-      <x:c r="J15" s="3"/>
-      <x:c r="K15" s="3"/>
-      <x:c r="L15" s="3"/>
-      <x:c r="M15" s="3"/>
-      <x:c r="N15" s="3"/>
-      <x:c r="O15" s="3"/>
-    </x:row>
-    <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A16" s="8"/>
-      <x:c r="B16" s="8"/>
-      <x:c r="C16" s="8"/>
-    </x:row>
-    <x:row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A17" s="9"/>
-      <x:c r="B17" s="9"/>
-      <x:c r="C17" s="9"/>
-    </x:row>
-    <x:row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A18" s="9"/>
-      <x:c r="B18" s="9"/>
-      <x:c r="C18" s="9"/>
-    </x:row>
-    <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A19" s="9"/>
-      <x:c r="B19" s="9"/>
-      <x:c r="C19" s="9"/>
-      <x:c r="D19" s="3"/>
-      <x:c r="E19" s="3"/>
-    </x:row>
-    <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A20" s="9"/>
-      <x:c r="B20" s="9"/>
-      <x:c r="C20" s="9"/>
-    </x:row>
-    <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A21" s="9"/>
-      <x:c r="B21" s="9"/>
-      <x:c r="C21" s="9"/>
-    </x:row>
-    <x:row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A22" s="9"/>
-      <x:c r="B22" s="9"/>
-      <x:c r="C22" s="9"/>
-    </x:row>
-    <x:row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A23" s="9"/>
-      <x:c r="B23" s="9"/>
-      <x:c r="C23" s="9"/>
-    </x:row>
-    <x:row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A24" s="9"/>
-      <x:c r="B24" s="9"/>
-      <x:c r="C24" s="9"/>
-    </x:row>
-    <x:row r="25" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A25" s="9"/>
-      <x:c r="B25" s="9"/>
-      <x:c r="C25" s="9"/>
-      <x:c r="E25" s="3"/>
-    </x:row>
-    <x:row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A26" s="10"/>
-      <x:c r="B26" s="10"/>
-      <x:c r="C26" s="10"/>
-      <x:c r="E26" s="3"/>
-    </x:row>
-    <x:row r="27" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A27" s="10"/>
-      <x:c r="B27" s="10"/>
-      <x:c r="C27" s="10"/>
-      <x:c r="E27" s="3"/>
-    </x:row>
-    <x:row r="28" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A28" s="10"/>
-      <x:c r="B28" s="10"/>
-      <x:c r="C28" s="10"/>
-      <x:c r="E28" s="3"/>
-    </x:row>
-    <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A29" s="10"/>
-      <x:c r="B29" s="10"/>
-      <x:c r="C29" s="10"/>
-    </x:row>
-    <x:row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A30" s="10"/>
-      <x:c r="B30" s="10"/>
-      <x:c r="C30" s="10"/>
-    </x:row>
-    <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A31" s="10"/>
-      <x:c r="B31" s="10"/>
-      <x:c r="C31" s="10"/>
-    </x:row>
-    <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A32" s="11"/>
-      <x:c r="B32" s="11"/>
-      <x:c r="C32" s="11"/>
-    </x:row>
-    <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A33" s="11"/>
-      <x:c r="B33" s="11"/>
-      <x:c r="C33" s="11"/>
-    </x:row>
-    <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A34" s="11"/>
-      <x:c r="B34" s="11"/>
-      <x:c r="C34" s="11"/>
-    </x:row>
-    <x:row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A35" s="11"/>
-      <x:c r="B35" s="11"/>
-      <x:c r="C35" s="11"/>
+      <x:c r="A15" s="12"/>
+      <x:c r="B15" s="12"/>
+      <x:c r="C15" s="12"/>
+      <x:c r="D15" s="2"/>
+      <x:c r="E15" s="2"/>
+      <x:c r="F15" s="2"/>
+      <x:c r="G15" s="2"/>
+      <x:c r="H15" s="2"/>
+      <x:c r="I15" s="2"/>
+      <x:c r="J15" s="2"/>
+      <x:c r="K15" s="2"/>
+      <x:c r="L15" s="2"/>
+      <x:c r="M15" s="2"/>
+      <x:c r="N15" s="2"/>
+      <x:c r="O15" s="2"/>
+    </x:row>
+    <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A16" s="3"/>
+      <x:c r="B16" s="3"/>
+      <x:c r="C16" s="3"/>
+      <x:c r="D16" s="7"/>
+      <x:c r="E16" s="2"/>
+      <x:c r="F16" s="7"/>
+    </x:row>
+    <x:row r="17" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A17" s="3"/>
+      <x:c r="B17" s="3"/>
+      <x:c r="C17" s="3"/>
+      <x:c r="D17" s="7"/>
+      <x:c r="E17" s="2"/>
+      <x:c r="F17" s="7"/>
+    </x:row>
+    <x:row r="18" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A18" s="3"/>
+      <x:c r="B18" s="3"/>
+      <x:c r="C18" s="3"/>
+      <x:c r="D18" s="7"/>
+      <x:c r="E18" s="2"/>
+      <x:c r="F18" s="7"/>
+    </x:row>
+    <x:row r="19" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A19" s="3"/>
+      <x:c r="B19" s="3"/>
+      <x:c r="C19" s="3"/>
+      <x:c r="D19" s="2"/>
+      <x:c r="E19" s="2"/>
+      <x:c r="F19" s="7"/>
+    </x:row>
+    <x:row r="20" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A20" s="3"/>
+      <x:c r="B20" s="3"/>
+      <x:c r="C20" s="3"/>
+      <x:c r="D20" s="7"/>
+      <x:c r="E20" s="2"/>
+      <x:c r="F20" s="7"/>
+    </x:row>
+    <x:row r="21" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A21" s="3"/>
+      <x:c r="B21" s="3"/>
+      <x:c r="C21" s="3"/>
+      <x:c r="D21" s="7"/>
+      <x:c r="E21" s="2"/>
+      <x:c r="F21" s="7"/>
+    </x:row>
+    <x:row r="22" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A22" s="3"/>
+      <x:c r="B22" s="3"/>
+      <x:c r="C22" s="3"/>
+      <x:c r="D22" s="7"/>
+      <x:c r="E22" s="2"/>
+      <x:c r="F22" s="7"/>
+    </x:row>
+    <x:row r="23" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A23" s="3"/>
+      <x:c r="B23" s="3"/>
+      <x:c r="C23" s="3"/>
+      <x:c r="D23" s="7"/>
+      <x:c r="E23" s="2"/>
+      <x:c r="F23" s="7"/>
+    </x:row>
+    <x:row r="24" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A24" s="3"/>
+      <x:c r="B24" s="3"/>
+      <x:c r="C24" s="3"/>
+      <x:c r="D24" s="7"/>
+      <x:c r="E24" s="2"/>
+      <x:c r="F24" s="7"/>
+    </x:row>
+    <x:row r="25" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A25" s="3"/>
+      <x:c r="B25" s="3"/>
+      <x:c r="C25" s="3"/>
+      <x:c r="D25" s="7"/>
+      <x:c r="E25" s="2"/>
+      <x:c r="F25" s="7"/>
+    </x:row>
+    <x:row r="26" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A26" s="4"/>
+      <x:c r="B26" s="4"/>
+      <x:c r="C26" s="4"/>
+      <x:c r="D26" s="7"/>
+      <x:c r="E26" s="2"/>
+      <x:c r="F26" s="7"/>
+    </x:row>
+    <x:row r="27" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A27" s="4"/>
+      <x:c r="B27" s="4"/>
+      <x:c r="C27" s="4"/>
+      <x:c r="D27" s="7"/>
+      <x:c r="E27" s="2"/>
+      <x:c r="F27" s="7"/>
+    </x:row>
+    <x:row r="28" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A28" s="4"/>
+      <x:c r="B28" s="4"/>
+      <x:c r="C28" s="4"/>
+      <x:c r="D28" s="7"/>
+      <x:c r="E28" s="2"/>
+      <x:c r="F28" s="7"/>
+    </x:row>
+    <x:row r="29" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A29" s="4"/>
+      <x:c r="B29" s="4"/>
+      <x:c r="C29" s="4"/>
+      <x:c r="D29" s="7"/>
+      <x:c r="E29" s="2"/>
+      <x:c r="F29" s="7"/>
+    </x:row>
+    <x:row r="30" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A30" s="4"/>
+      <x:c r="B30" s="4"/>
+      <x:c r="C30" s="4"/>
+      <x:c r="D30" s="7"/>
+      <x:c r="E30" s="2"/>
+      <x:c r="F30" s="7"/>
+    </x:row>
+    <x:row r="31" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A31" s="4"/>
+      <x:c r="B31" s="4"/>
+      <x:c r="C31" s="4"/>
+      <x:c r="D31" s="7"/>
+      <x:c r="E31" s="2"/>
+      <x:c r="F31" s="7"/>
+    </x:row>
+    <x:row r="32" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A32" s="5"/>
+      <x:c r="B32" s="5"/>
+      <x:c r="C32" s="5"/>
+      <x:c r="D32" s="7"/>
+      <x:c r="E32" s="2"/>
+      <x:c r="F32" s="7"/>
+    </x:row>
+    <x:row r="33" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A33" s="5"/>
+      <x:c r="B33" s="5"/>
+      <x:c r="C33" s="5"/>
+      <x:c r="D33" s="7"/>
+      <x:c r="E33" s="2"/>
+      <x:c r="F33" s="7"/>
+    </x:row>
+    <x:row r="34" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A34" s="5"/>
+      <x:c r="B34" s="5"/>
+      <x:c r="C34" s="5"/>
+      <x:c r="D34" s="7"/>
+      <x:c r="E34" s="2"/>
+      <x:c r="F34" s="7"/>
+    </x:row>
+    <x:row r="35" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A35" s="5"/>
+      <x:c r="B35" s="5"/>
+      <x:c r="C35" s="5"/>
+      <x:c r="D35" s="7"/>
+      <x:c r="E35" s="2"/>
+      <x:c r="F35" s="7"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>
@@ -1780,7 +2237,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>